--- a/output/pdf_financials_xlsx/STAR.xlsx
+++ b/output/pdf_financials_xlsx/STAR.xlsx
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.11312</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.123737</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.334721</v>
       </c>
     </row>
     <row r="93">
@@ -3067,7 +3067,11 @@
           <t>Share purchase warrants reserve 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3098,7 +3102,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3350,7 +3358,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>0.11312</v>
       </c>

--- a/output/pdf_financials_xlsx/STAR.xlsx
+++ b/output/pdf_financials_xlsx/STAR.xlsx
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.03971</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.010369</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.022138</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.03971</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.010369</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.022138</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.039723</v>
+        <v>1.3e-05</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.010382</v>
+        <v>1.3e-05</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.022151</v>
+        <v>1.3e-05</v>
       </c>
     </row>
     <row r="49">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
